--- a/jogos_2025-01-17.xlsx
+++ b/jogos_2025-01-17.xlsx
@@ -1546,19 +1546,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T9" t="n">
         <v>3.5</v>
       </c>
-      <c r="N9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA9" t="n">
         <v>4</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AB9" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['15', '85']</t>
+          <t>['44', '49']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45674.41666666666</v>
@@ -1675,16 +1675,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -1693,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,55 +1701,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
         <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.5</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="U10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X10" t="n">
         <v>4</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.45</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AC10" t="n">
         <v>1.8</v>
@@ -1759,25 +1759,25 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['15', '85']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45674.41666666666</v>
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
         <v>2.1</v>
@@ -1848,65 +1848,65 @@
         <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>2.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['45', '71']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['16', '81']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45674.41666666666</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
         <v>3.25</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.5</v>
       </c>
-      <c r="S12" t="n">
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.5</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="AB12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['45', '71']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['16', '81']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>2.75</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['44', '49']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45674.41666666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Şanlıurfaspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Ankaragücü</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>3.57</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>3.37</v>
       </c>
       <c r="N16" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="O16" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="T16" t="n">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="X16" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AD16" t="n">
         <v>2</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['45+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45674.58333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Şanlıurfaspor</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ankaragücü</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.57</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.37</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1.95</v>
       </c>
-      <c r="O17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.65</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AD17" t="n">
         <v>2</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+5']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45674.58333333334</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.85</v>
+        <v>2.31</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>1.84</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
         <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '60']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['69', '72']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45674.60416666666</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.31</v>
+        <v>3.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>1.84</v>
       </c>
       <c r="O22" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
         <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="X22" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['41', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['69', '72']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45674.60416666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>2.13</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>6.8</v>
+        <v>3.55</v>
       </c>
       <c r="O24" t="n">
-        <v>1.99</v>
+        <v>2.7</v>
       </c>
       <c r="P24" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="X24" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>['9', '35', '76', '81']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45674.625</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.13</v>
+        <v>1.44</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="O25" t="n">
-        <v>2.7</v>
+        <v>1.99</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['9', '35', '76', '81']</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45674.625</v>
@@ -3997,109 +3997,109 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y28" t="n">
         <v>2</v>
       </c>
-      <c r="H28" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Z28" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['27', '60']</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['55', '62']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45674.64583333334</v>
@@ -4126,19 +4126,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N29" t="n">
-        <v>5.75</v>
+        <v>2.7</v>
       </c>
       <c r="O29" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="S29" t="n">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="T29" t="n">
-        <v>2.99</v>
+        <v>3.26</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X29" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['27', '60']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['55', '62']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AJ29" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45674.64583333334</v>
@@ -4255,19 +4255,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M30" t="n">
-        <v>4.29</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>4.32</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.22</v>
       </c>
-      <c r="S30" t="n">
-        <v>4</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U30" t="n">
+      <c r="X30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.67</v>
       </c>
-      <c r="V30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z30" t="n">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="AA30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>2</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>['13']</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45674.66666666666</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Martigues</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N31" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="P31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q31" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>5.5</v>
       </c>
       <c r="R31" t="n">
         <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="U31" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
         <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AA31" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30', '77']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.5</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.45</v>
+        <v>2.55</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3.2</v>
+        <v>1.62</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45674.66666666666</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4528,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.95</v>
+        <v>1.95</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N32" t="n">
-        <v>2.49</v>
+        <v>3.9</v>
       </c>
       <c r="O32" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="P32" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="R32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z32" t="n">
         <v>1.53</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U32" t="n">
+      <c r="AA32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.28</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45674.66666666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,91 +4642,91 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>KMSK Deinze</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['5', '43', '45', '58']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45674.66666666666</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,22 +4771,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.9</v>
+        <v>1.45</v>
       </c>
       <c r="M34" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.55</v>
+        <v>6.25</v>
       </c>
       <c r="O34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S34" t="n">
         <v>3.45</v>
       </c>
-      <c r="P34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X34" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y34" t="n">
         <v>1.5</v>
       </c>
-      <c r="S34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y34" t="n">
+      <c r="Z34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA34" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AB34" t="n">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['70', '83']</t>
+          <t>['17', '56', '67']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.2</v>
+        <v>1.42</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45674.66666666666</v>
@@ -4900,23 +4900,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
         <v>3</v>
       </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="M35" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N35" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="O35" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="P35" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="U35" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X35" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['17', '56', '67']</t>
+          <t>['5', '43', '45', '58']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG35" t="n">
         <v>1.11</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45674.66666666666</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,19 +5029,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="M36" t="n">
-        <v>3.65</v>
+        <v>4.29</v>
       </c>
       <c r="N36" t="n">
-        <v>3.45</v>
+        <v>4.32</v>
       </c>
       <c r="O36" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="P36" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="U36" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V36" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X36" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
         <v>1.22</v>
       </c>
-      <c r="X36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z36" t="n">
+      <c r="AH36" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA36" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['5', '71', '90+5']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AI36" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45674.66666666666</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S37" t="n">
         <v>3</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q37" t="n">
+      <c r="T37" t="n">
         <v>2.75</v>
       </c>
-      <c r="R37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.4</v>
-      </c>
       <c r="U37" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W37" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X37" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['31', '82']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AG37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI37" t="n">
         <v>1.62</v>
       </c>
-      <c r="AH37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AJ37" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45674.66666666666</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,28 +5313,28 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>3.7</v>
+        <v>2.47</v>
       </c>
       <c r="O38" t="n">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="P38" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T38" t="n">
         <v>2.75</v>
@@ -5343,53 +5343,53 @@
         <v>1.4</v>
       </c>
       <c r="V38" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W38" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X38" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD38" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['31', '82']</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['20', '61', '70']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45674.66666666666</v>
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,22 +5442,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N39" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="O39" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R39" t="n">
         <v>1.33</v>
@@ -5466,10 +5466,10 @@
         <v>3.1</v>
       </c>
       <c r="T39" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="U39" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V39" t="n">
         <v>1.04</v>
@@ -5493,32 +5493,32 @@
         <v>1.48</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['30', '77']</t>
-        </is>
-      </c>
       <c r="AG39" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45674.66666666666</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5560,7 +5560,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC40" t="n">
         <v>1.95</v>
       </c>
-      <c r="M40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N40" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S40" t="n">
+      <c r="AD40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI40" t="n">
         <v>2.25</v>
       </c>
-      <c r="T40" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>['9']</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ40" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45674.66666666666</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,22 +5674,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N41" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O41" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R41" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="T41" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="U41" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="V41" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W41" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="X41" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.62</v>
+        <v>4.33</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.35</v>
+        <v>1.77</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['70', '83']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AG41" t="n">
         <v>1.48</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45674.66666666666</v>
@@ -5803,109 +5803,109 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KMSK Deinze</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '38', '45', '90+3']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45674.66666666666</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,69 +5932,69 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Martigues</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S43" t="n">
         <v>3</v>
       </c>
-      <c r="J43" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N43" t="n">
-        <v>5</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>5</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.9</v>
-      </c>
       <c r="T43" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="U43" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W43" t="n">
         <v>1.25</v>
       </c>
       <c r="X43" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="Y43" t="n">
         <v>1.85</v>
@@ -6003,38 +6003,38 @@
         <v>1.89</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AC43" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD43" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD43" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['27', '38', '45', '90+3']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG43" t="n">
         <v>1.12</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45674.66666666666</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,22 +6061,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="M44" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="O44" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="P44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z44" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AA44" t="n">
-        <v>3.35</v>
+        <v>2.65</v>
       </c>
       <c r="AB44" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['5', '71', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC44" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH44" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ44" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45674.66666666666</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,25 +6190,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N45" t="n">
-        <v>2.47</v>
+        <v>2.95</v>
       </c>
       <c r="O45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X45" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA45" t="n">
         <v>3.35</v>
       </c>
-      <c r="P45" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AB45" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>['20', '61', '70']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AI45" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45674.66666666666</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,22 +6319,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -6345,65 +6345,65 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O46" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X46" t="n">
         <v>2.4</v>
       </c>
-      <c r="M46" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="O46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R46" t="n">
+      <c r="Y46" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Z46" t="n">
         <v>1.5</v>
       </c>
-      <c r="S46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X46" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AA46" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -6412,16 +6412,16 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45674.6875</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,25 +6448,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -6474,22 +6474,22 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="M47" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="N47" t="n">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="O47" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="R47" t="n">
         <v>1.44</v>
@@ -6498,59 +6498,59 @@
         <v>2.63</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>['17', '52', '85']</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH47" t="n">
         <v>1.33</v>
       </c>
-      <c r="V47" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X47" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>['67', '81']</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AI47" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45674.6875</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,25 +6577,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="M48" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="O48" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="P48" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U48" t="n">
         <v>1.29</v>
       </c>
-      <c r="S48" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X48" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z48" t="n">
         <v>1.57</v>
       </c>
-      <c r="V48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X48" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.57</v>
-      </c>
       <c r="AA48" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ48" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>['18', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>2.05</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45674.6875</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6721,10 +6721,10 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,43 +6732,43 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M49" t="n">
         <v>3.4</v>
       </c>
-      <c r="M49" t="n">
-        <v>3.3</v>
-      </c>
       <c r="N49" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="P49" t="n">
         <v>2.05</v>
       </c>
       <c r="Q49" t="n">
+        <v>4</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" t="n">
         <v>2.63</v>
       </c>
-      <c r="R49" t="n">
+      <c r="U49" t="n">
         <v>1.44</v>
       </c>
-      <c r="S49" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V49" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W49" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="X49" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="Y49" t="n">
         <v>2.1</v>
@@ -6777,38 +6777,38 @@
         <v>1.7</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="AB49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>['6', '21', '53']</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
         <v>1.27</v>
       </c>
-      <c r="AC49" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>['24']</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>['17', '52', '85']</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AH49" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45674.6875</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,25 +6835,25 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="P50" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="Q50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S50" t="n">
         <v>3.5</v>
       </c>
-      <c r="R50" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T50" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="U50" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="V50" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W50" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="X50" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="Z50" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB50" t="n">
         <v>1.65</v>
       </c>
-      <c r="AA50" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AC50" t="n">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['18', '90+2']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['31', '62']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45674.6875</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,109 +7093,109 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N52" t="n">
         <v>3</v>
       </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="M52" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T52" t="n">
         <v>3.1</v>
       </c>
-      <c r="O52" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>4</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S52" t="n">
-        <v>3</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U52" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="V52" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W52" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="X52" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="Y52" t="n">
         <v>2.1</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AD52" t="n">
         <v>1.8</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['6', '21', '53']</t>
+          <t>['31', '62']</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45674.6875</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="M53" t="n">
         <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="O53" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P53" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="R53" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="S53" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="T53" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="V53" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W53" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="X53" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AA53" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AC53" t="n">
         <v>2.2</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
       <c r="AG53" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45674.6875</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,19 +7351,19 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="M54" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="N54" t="n">
-        <v>1.7</v>
+        <v>3.25</v>
       </c>
       <c r="O54" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="R54" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S54" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T54" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U54" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V54" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W54" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="X54" t="n">
-        <v>3.2</v>
+        <v>2.43</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AA54" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['67', '81']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AI54" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45674.6875</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,22 +7480,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H55" t="n">
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
@@ -7506,83 +7506,83 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="M55" t="n">
+        <v>4</v>
+      </c>
+      <c r="N55" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>6</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X55" t="n">
         <v>3.6</v>
       </c>
-      <c r="N55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O55" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X55" t="n">
-        <v>3.95</v>
-      </c>
       <c r="Y55" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['25', '60', '73']</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AJ55" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45674.69791666666</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,25 +7738,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>['34', '56']</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
         <v>1.57</v>
       </c>
-      <c r="M57" t="n">
-        <v>4</v>
-      </c>
-      <c r="N57" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O57" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P57" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>6</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X57" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD57" t="n">
+      <c r="AH57" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ57" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>['25', '60', '73']</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>['33']</t>
-        </is>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>3.25</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45674.69791666666</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,25 +7867,25 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.15</v>
+        <v>2.05</v>
       </c>
       <c r="M58" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N58" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="O58" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="P58" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q58" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S58" t="n">
         <v>3.1</v>
       </c>
-      <c r="R58" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S58" t="n">
-        <v>2.63</v>
-      </c>
       <c r="T58" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="U58" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="V58" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W58" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="X58" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="Y58" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Z58" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI58" t="n">
         <v>1.73</v>
       </c>
-      <c r="AA58" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>['34', '56']</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG58" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ58" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45674.69791666666</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,22 +8512,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -8538,65 +8538,65 @@
         </is>
       </c>
       <c r="L63" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M63" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X63" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB63" t="n">
         <v>1.2</v>
       </c>
-      <c r="M63" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N63" t="n">
-        <v>14</v>
-      </c>
-      <c r="O63" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P63" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>11</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S63" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T63" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X63" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC63" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>['11', '36', '67', '80']</t>
+          <t>['2', '53', '81']</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -8605,16 +8605,16 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AH63" t="n">
-        <v>4.4</v>
+        <v>1.61</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.14</v>
+        <v>1.83</v>
       </c>
       <c r="AJ63" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45674.71875</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,22 +8641,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -8667,65 +8667,65 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.24</v>
+        <v>1.2</v>
       </c>
       <c r="M64" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="N64" t="n">
-        <v>3.45</v>
+        <v>14</v>
       </c>
       <c r="O64" t="n">
-        <v>2.87</v>
+        <v>1.62</v>
       </c>
       <c r="P64" t="n">
-        <v>1.98</v>
+        <v>2.75</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.75</v>
+        <v>11</v>
       </c>
       <c r="R64" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="S64" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="T64" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="U64" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="V64" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="W64" t="n">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="X64" t="n">
-        <v>2.75</v>
+        <v>4.15</v>
       </c>
       <c r="Y64" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA64" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z64" t="n">
+      <c r="AB64" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD64" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA64" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>['2', '53', '81']</t>
+          <t>['11', '36', '67', '80']</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -8734,16 +8734,16 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.33</v>
+        <v>1.03</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.61</v>
+        <v>4.4</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.83</v>
+        <v>1.14</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45674.71875</v>
